--- a/training_result/90/0/cr/parameters_4.xlsx
+++ b/training_result/90/0/cr/parameters_4.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C76"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,7 +469,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>6.803</v>
+        <v>12.0149</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2028</v>
+        <v>0.2019</v>
       </c>
     </row>
     <row r="6">
@@ -508,7 +508,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>-34.7021</v>
+        <v>-28.3961</v>
       </c>
     </row>
     <row r="8">
@@ -534,7 +534,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.2569</v>
+        <v>-1.2495</v>
       </c>
     </row>
     <row r="10">
@@ -547,7 +547,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>-23.4469</v>
+        <v>-38.4475</v>
       </c>
     </row>
     <row r="11">
@@ -586,7 +586,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>-26.9999</v>
+        <v>-10.2136</v>
       </c>
     </row>
     <row r="14">
@@ -625,7 +625,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>-22.7922</v>
+        <v>-1.4539</v>
       </c>
     </row>
     <row r="17">
@@ -664,7 +664,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1.002</v>
+        <v>1.8873</v>
       </c>
     </row>
     <row r="20">
@@ -703,7 +703,7 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>3.0055</v>
+        <v>0.4599</v>
       </c>
     </row>
     <row r="23">
@@ -742,7 +742,7 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>-16.8709</v>
+        <v>-5.0549</v>
       </c>
     </row>
     <row r="26">
@@ -781,7 +781,7 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>11.2631</v>
+        <v>28.2024</v>
       </c>
     </row>
     <row r="29">
@@ -820,7 +820,7 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>-16.455</v>
+        <v>-4.4769</v>
       </c>
     </row>
     <row r="32">
@@ -859,7 +859,7 @@
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>-4.3063</v>
+        <v>-4.3398</v>
       </c>
     </row>
     <row r="35">
@@ -898,7 +898,7 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>22.717</v>
+        <v>16.4165</v>
       </c>
     </row>
     <row r="38">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4278</v>
+        <v>0.4302</v>
       </c>
     </row>
     <row r="39">
@@ -937,7 +937,7 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>16.81</v>
+        <v>12.8965</v>
       </c>
     </row>
     <row r="41">
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>-3.8874</v>
+        <v>-12.4994</v>
       </c>
     </row>
     <row r="44">
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>-23.3827</v>
+        <v>-21.0199</v>
       </c>
     </row>
     <row r="47">
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>-17.5258</v>
+        <v>-3.4055</v>
       </c>
     </row>
     <row r="50">
@@ -1067,7 +1067,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.7114</v>
+        <v>-0.7115</v>
       </c>
     </row>
     <row r="51">
@@ -1093,7 +1093,7 @@
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>2.01</v>
+        <v>11.3444</v>
       </c>
     </row>
     <row r="53">
@@ -1132,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>-5.2569</v>
+        <v>-13.2169</v>
       </c>
     </row>
     <row r="56">
@@ -1145,7 +1145,7 @@
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>0.2293</v>
+        <v>0.2309</v>
       </c>
     </row>
     <row r="57">
@@ -1171,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>8.8049</v>
+        <v>10.4373</v>
       </c>
     </row>
     <row r="59">
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="C61" t="n">
-        <v>-6.5185</v>
+        <v>-6.4576</v>
       </c>
     </row>
     <row r="62">
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>-5.9899</v>
+        <v>-6.766</v>
       </c>
     </row>
     <row r="65">
@@ -1262,7 +1262,7 @@
         <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>0.2456</v>
+        <v>0.2455</v>
       </c>
     </row>
     <row r="66">
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>1.1032</v>
+        <v>0.3561</v>
       </c>
     </row>
     <row r="68">
@@ -1327,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="C70" t="n">
-        <v>-4.0009</v>
+        <v>-5.4493</v>
       </c>
     </row>
     <row r="71">
@@ -1398,14 +1398,92 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>第26站-other</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>第27站-1</t>
         </is>
       </c>
-      <c r="B76" t="n">
-        <v>0</v>
-      </c>
-      <c r="C76" t="n">
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" t="n">
         <v>-2.6563</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>第27站-2</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>第27站-other</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>第28站-1</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>第28站-2</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>第28站-other</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
